--- a/public/data/PLA0926_DGFM SEPTIEMBRE.xlsx
+++ b/public/data/PLA0926_DGFM SEPTIEMBRE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026\ESFM\INSTITUCIONALIZACIÓN\BASE DE DATOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A69D76-F30F-4232-BF0D-8AECF3008CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E54CCD-723F-4821-8349-2B6D8968796A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -311,7 +311,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B86AB403-5F11-48E4-8035-242721181A55}" name="Tabla1" displayName="Tabla1" ref="A1:E2269" totalsRowShown="0">
-  <autoFilter ref="A1:E2269" xr:uid="{B86AB403-5F11-48E4-8035-242721181A55}"/>
+  <autoFilter ref="A1:E2269" xr:uid="{B86AB403-5F11-48E4-8035-242721181A55}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="1"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E2269">
     <sortCondition ref="A1:A2269"/>
   </sortState>
@@ -1142,7 +1148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>22</v>
       </c>
@@ -1227,7 +1233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>22</v>
       </c>
@@ -1261,7 +1267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>22</v>
       </c>
@@ -1329,7 +1335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>22</v>
       </c>
@@ -1363,7 +1369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -1380,7 +1386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>22</v>
       </c>
@@ -1397,7 +1403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>22</v>
       </c>
@@ -1414,7 +1420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>22</v>
       </c>
@@ -1431,7 +1437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>22</v>
       </c>
@@ -1448,7 +1454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>22</v>
       </c>
@@ -1465,7 +1471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>22</v>
       </c>
@@ -1533,7 +1539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>22</v>
       </c>
@@ -1550,7 +1556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>22</v>
       </c>
@@ -1567,7 +1573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>22</v>
       </c>
@@ -1584,7 +1590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>22</v>
       </c>
@@ -1601,7 +1607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>22</v>
       </c>
@@ -1635,7 +1641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>22</v>
       </c>
@@ -1652,7 +1658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>22</v>
       </c>
@@ -1669,7 +1675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>22</v>
       </c>
@@ -1686,7 +1692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>22</v>
       </c>
@@ -1703,7 +1709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>22</v>
       </c>
@@ -1720,7 +1726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>22</v>
       </c>
@@ -1737,7 +1743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>22</v>
       </c>
@@ -1771,7 +1777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>22</v>
       </c>
@@ -1788,7 +1794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>22</v>
       </c>
@@ -1822,7 +1828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>22</v>
       </c>
@@ -1941,7 +1947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>22</v>
       </c>
@@ -2281,7 +2287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>22</v>
       </c>
@@ -2315,7 +2321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>22</v>
       </c>
@@ -2332,7 +2338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>22</v>
       </c>
@@ -2383,7 +2389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>22</v>
       </c>
@@ -2553,7 +2559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>22</v>
       </c>
@@ -2570,7 +2576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>22</v>
       </c>
@@ -2587,7 +2593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>22</v>
       </c>
@@ -2672,7 +2678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>22</v>
       </c>
@@ -2689,7 +2695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>22</v>
       </c>
@@ -2706,7 +2712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>22</v>
       </c>
@@ -2723,7 +2729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>22</v>
       </c>
@@ -2893,7 +2899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>22</v>
       </c>
@@ -3063,7 +3069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>22</v>
       </c>
@@ -3114,7 +3120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>5</v>
       </c>
@@ -3165,7 +3171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>5</v>
       </c>
@@ -3182,7 +3188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>5</v>
       </c>
@@ -3199,7 +3205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>5</v>
       </c>
@@ -3250,7 +3256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>5</v>
       </c>
@@ -3590,7 +3596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>5</v>
       </c>
@@ -3624,7 +3630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>5</v>
       </c>
@@ -3658,7 +3664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>5</v>
       </c>
@@ -3675,7 +3681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>5</v>
       </c>
@@ -3692,7 +3698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>5</v>
       </c>
@@ -3726,7 +3732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>5</v>
       </c>
@@ -3760,7 +3766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>5</v>
       </c>
@@ -3794,7 +3800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>5</v>
       </c>
@@ -3811,7 +3817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>5</v>
       </c>
@@ -3845,7 +3851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>5</v>
       </c>
@@ -3913,7 +3919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>5</v>
       </c>
@@ -3947,7 +3953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>5</v>
       </c>
@@ -4066,7 +4072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>5</v>
       </c>
@@ -4100,7 +4106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>5</v>
       </c>
@@ -4117,7 +4123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>5</v>
       </c>
@@ -4168,7 +4174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>5</v>
       </c>
@@ -4253,7 +4259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>5</v>
       </c>
@@ -4270,7 +4276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>5</v>
       </c>
@@ -4287,7 +4293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>5</v>
       </c>
@@ -4304,7 +4310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>5</v>
       </c>
@@ -4321,7 +4327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>5</v>
       </c>
@@ -4372,7 +4378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>5</v>
       </c>
@@ -4440,7 +4446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>5</v>
       </c>
@@ -4491,7 +4497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>5</v>
       </c>
@@ -4508,7 +4514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>5</v>
       </c>
@@ -4542,7 +4548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>5</v>
       </c>
@@ -4576,7 +4582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>5</v>
       </c>
@@ -4610,7 +4616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>5</v>
       </c>
@@ -4678,7 +4684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>5</v>
       </c>
@@ -4712,7 +4718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>5</v>
       </c>
@@ -4763,7 +4769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>5</v>
       </c>
@@ -4797,7 +4803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>5</v>
       </c>
@@ -4848,7 +4854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>5</v>
       </c>
@@ -4865,7 +4871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>5</v>
       </c>
@@ -4916,7 +4922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>5</v>
       </c>
@@ -4933,7 +4939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>5</v>
       </c>
@@ -4950,7 +4956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>5</v>
       </c>
@@ -5035,7 +5041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>5</v>
       </c>
@@ -5069,7 +5075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>5</v>
       </c>
@@ -5137,7 +5143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>5</v>
       </c>
@@ -5222,7 +5228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>5</v>
       </c>
@@ -5256,7 +5262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>5</v>
       </c>
@@ -5273,7 +5279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>5</v>
       </c>
@@ -5290,7 +5296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>5</v>
       </c>
@@ -5307,7 +5313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>5</v>
       </c>
@@ -5324,7 +5330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>5</v>
       </c>
@@ -5477,7 +5483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>5</v>
       </c>
@@ -5494,7 +5500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>5</v>
       </c>
@@ -5613,7 +5619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>5</v>
       </c>
@@ -6004,7 +6010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>5</v>
       </c>
@@ -6089,7 +6095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>5</v>
       </c>
@@ -6106,7 +6112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>5</v>
       </c>
@@ -6140,7 +6146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>5</v>
       </c>
@@ -6344,7 +6350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>17</v>
       </c>
@@ -6378,7 +6384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>17</v>
       </c>
@@ -6395,7 +6401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>17</v>
       </c>
@@ -6531,7 +6537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>17</v>
       </c>
@@ -6548,7 +6554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>17</v>
       </c>
@@ -6650,7 +6656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>17</v>
       </c>
@@ -6769,7 +6775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>17</v>
       </c>
@@ -6854,7 +6860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>17</v>
       </c>
@@ -6871,7 +6877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>17</v>
       </c>
@@ -6905,7 +6911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>17</v>
       </c>
@@ -6956,7 +6962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>17</v>
       </c>
@@ -7007,7 +7013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>17</v>
       </c>
@@ -7024,7 +7030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>17</v>
       </c>
@@ -7075,7 +7081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>17</v>
       </c>
@@ -7092,7 +7098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>17</v>
       </c>
@@ -7109,7 +7115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>17</v>
       </c>
@@ -7160,7 +7166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>17</v>
       </c>
@@ -7279,7 +7285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>17</v>
       </c>
@@ -7296,7 +7302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>17</v>
       </c>
@@ -7313,7 +7319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>17</v>
       </c>
@@ -7330,7 +7336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>17</v>
       </c>
@@ -7415,7 +7421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>17</v>
       </c>
@@ -7568,7 +7574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>17</v>
       </c>
@@ -7687,7 +7693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>17</v>
       </c>
@@ -7704,7 +7710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>17</v>
       </c>
@@ -7738,7 +7744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>17</v>
       </c>
@@ -7772,7 +7778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>17</v>
       </c>
@@ -7806,7 +7812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>17</v>
       </c>
@@ -7823,7 +7829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>17</v>
       </c>
@@ -7840,7 +7846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>17</v>
       </c>
@@ -7874,7 +7880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>17</v>
       </c>
@@ -7908,7 +7914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>17</v>
       </c>
@@ -7959,7 +7965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>17</v>
       </c>
@@ -8129,7 +8135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>17</v>
       </c>
@@ -8146,7 +8152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>17</v>
       </c>
@@ -8180,7 +8186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>17</v>
       </c>
@@ -8197,7 +8203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>17</v>
       </c>
@@ -8214,7 +8220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>17</v>
       </c>
@@ -8231,7 +8237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>17</v>
       </c>
@@ -8316,7 +8322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>17</v>
       </c>
@@ -8367,7 +8373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>17</v>
       </c>
@@ -8418,7 +8424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>17</v>
       </c>
@@ -8486,7 +8492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>17</v>
       </c>
@@ -8520,7 +8526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>17</v>
       </c>
@@ -8554,7 +8560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>17</v>
       </c>
@@ -8571,7 +8577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>17</v>
       </c>
@@ -8690,7 +8696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>17</v>
       </c>
@@ -8741,7 +8747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>17</v>
       </c>
@@ -8758,7 +8764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>17</v>
       </c>
@@ -8894,7 +8900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>17</v>
       </c>
@@ -8928,7 +8934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="491" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>17</v>
       </c>
@@ -8945,7 +8951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>17</v>
       </c>
@@ -8979,7 +8985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="494" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>17</v>
       </c>
@@ -8996,7 +9002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="495" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>17</v>
       </c>
@@ -9013,7 +9019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="496" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>17</v>
       </c>
@@ -9030,7 +9036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>17</v>
       </c>
@@ -9047,7 +9053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>17</v>
       </c>
@@ -9081,7 +9087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>17</v>
       </c>
@@ -9115,7 +9121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>17</v>
       </c>
@@ -9132,7 +9138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>17</v>
       </c>
@@ -9183,7 +9189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>17</v>
       </c>
@@ -9200,7 +9206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>17</v>
       </c>
@@ -9217,7 +9223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>17</v>
       </c>
@@ -9251,7 +9257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="510" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>17</v>
       </c>
@@ -9302,7 +9308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="513" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>17</v>
       </c>
@@ -9319,7 +9325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>17</v>
       </c>
@@ -9336,7 +9342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="515" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>17</v>
       </c>
@@ -9353,7 +9359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="516" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>17</v>
       </c>
@@ -9370,7 +9376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>17</v>
       </c>
@@ -9421,7 +9427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="520" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>17</v>
       </c>
@@ -9438,7 +9444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="521" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>17</v>
       </c>
@@ -9455,7 +9461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="522" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>17</v>
       </c>
@@ -9506,7 +9512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="525" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>17</v>
       </c>
@@ -9523,7 +9529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="526" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>17</v>
       </c>
@@ -9557,7 +9563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="528" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>17</v>
       </c>
@@ -9608,7 +9614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="531" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>17</v>
       </c>
@@ -9659,7 +9665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="534" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>17</v>
       </c>
@@ -9676,7 +9682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>17</v>
       </c>
@@ -9693,7 +9699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="536" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>17</v>
       </c>
@@ -9710,7 +9716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="537" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>17</v>
       </c>
@@ -9727,7 +9733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="538" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>17</v>
       </c>
@@ -9744,7 +9750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="539" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>17</v>
       </c>
@@ -9761,7 +9767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="540" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>17</v>
       </c>
@@ -9778,7 +9784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="541" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>17</v>
       </c>
@@ -9795,7 +9801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="542" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>17</v>
       </c>
@@ -9812,7 +9818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="543" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>17</v>
       </c>
@@ -9829,7 +9835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="544" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>17</v>
       </c>
@@ -9914,7 +9920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="549" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>17</v>
       </c>
@@ -10016,7 +10022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="555" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>17</v>
       </c>
@@ -10050,7 +10056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="557" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>17</v>
       </c>
@@ -10135,7 +10141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="562" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>17</v>
       </c>
@@ -10203,7 +10209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="566" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>17</v>
       </c>
@@ -10220,7 +10226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="567" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>17</v>
       </c>
@@ -10237,7 +10243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="568" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>17</v>
       </c>
@@ -10441,7 +10447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="580" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>17</v>
       </c>
@@ -10645,7 +10651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="592" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>17</v>
       </c>
@@ -10798,7 +10804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="601" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>17</v>
       </c>
@@ -10866,7 +10872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="605" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>17</v>
       </c>
@@ -10883,7 +10889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="606" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>17</v>
       </c>
@@ -11087,7 +11093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="618" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>17</v>
       </c>
@@ -11121,7 +11127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="620" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>17</v>
       </c>
@@ -11172,7 +11178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="623" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>17</v>
       </c>
@@ -11240,7 +11246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="627" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>15</v>
       </c>
@@ -11342,7 +11348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="633" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>15</v>
       </c>
@@ -11427,7 +11433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="638" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>15</v>
       </c>
@@ -11444,7 +11450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="639" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>15</v>
       </c>
@@ -11614,7 +11620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="649" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>15</v>
       </c>
@@ -11665,7 +11671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="652" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>15</v>
       </c>
@@ -11733,7 +11739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="656" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>15</v>
       </c>
@@ -11835,7 +11841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="662" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>15</v>
       </c>
@@ -11852,7 +11858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="663" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>15</v>
       </c>
@@ -11920,7 +11926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="667" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>15</v>
       </c>
@@ -11937,7 +11943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="668" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>15</v>
       </c>
@@ -11988,7 +11994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="671" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>15</v>
       </c>
@@ -12141,7 +12147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="680" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>15</v>
       </c>
@@ -12175,7 +12181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="682" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>15</v>
       </c>
@@ -12192,7 +12198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="683" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>15</v>
       </c>
@@ -12243,7 +12249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="686" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>15</v>
       </c>
@@ -12260,7 +12266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="687" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>15</v>
       </c>
@@ -12481,7 +12487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="700" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>15</v>
       </c>
@@ -12600,7 +12606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="707" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>15</v>
       </c>
@@ -12634,7 +12640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="709" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>15</v>
       </c>
@@ -12651,7 +12657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="710" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>15</v>
       </c>
@@ -12668,7 +12674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="711" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>15</v>
       </c>
@@ -12719,7 +12725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="714" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>15</v>
       </c>
@@ -12855,7 +12861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="722" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>15</v>
       </c>
@@ -12940,7 +12946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="727" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>15</v>
       </c>
@@ -12974,7 +12980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="729" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>15</v>
       </c>
@@ -12991,7 +12997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="730" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>15</v>
       </c>
@@ -13008,7 +13014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="731" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>15</v>
       </c>
@@ -13025,7 +13031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="732" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>15</v>
       </c>
@@ -13042,7 +13048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="733" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>15</v>
       </c>
@@ -13059,7 +13065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="734" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>15</v>
       </c>
@@ -13076,7 +13082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="735" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>15</v>
       </c>
@@ -13127,7 +13133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="738" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>15</v>
       </c>
@@ -13178,7 +13184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="741" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>15</v>
       </c>
@@ -13195,7 +13201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="742" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>15</v>
       </c>
@@ -13229,7 +13235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="744" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>15</v>
       </c>
@@ -13246,7 +13252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="745" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>15</v>
       </c>
@@ -13263,7 +13269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="746" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>15</v>
       </c>
@@ -13280,7 +13286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="747" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>15</v>
       </c>
@@ -13297,7 +13303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="748" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>15</v>
       </c>
@@ -13314,7 +13320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="749" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>15</v>
       </c>
@@ -13331,7 +13337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="750" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>15</v>
       </c>
@@ -13348,7 +13354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="751" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>15</v>
       </c>
@@ -13518,7 +13524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="761" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>15</v>
       </c>
@@ -13535,7 +13541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="762" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>15</v>
       </c>
@@ -13603,7 +13609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="766" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>15</v>
       </c>
@@ -13620,7 +13626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="767" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>15</v>
       </c>
@@ -13637,7 +13643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="768" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>15</v>
       </c>
@@ -13654,7 +13660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="769" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>15</v>
       </c>
@@ -13739,7 +13745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="774" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>15</v>
       </c>
@@ -13841,7 +13847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="780" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>15</v>
       </c>
@@ -13875,7 +13881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="782" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>15</v>
       </c>
@@ -14062,7 +14068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="793" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>15</v>
       </c>
@@ -14113,7 +14119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="796" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>15</v>
       </c>
@@ -14147,7 +14153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="798" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>15</v>
       </c>
@@ -14215,7 +14221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="802" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>15</v>
       </c>
@@ -14334,7 +14340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="809" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>15</v>
       </c>
@@ -14368,7 +14374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="811" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>15</v>
       </c>
@@ -14385,7 +14391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="812" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>15</v>
       </c>
@@ -14402,7 +14408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="813" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>15</v>
       </c>
@@ -14419,7 +14425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="814" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>15</v>
       </c>
@@ -14436,7 +14442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="815" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>15</v>
       </c>
@@ -14572,7 +14578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="823" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>15</v>
       </c>
@@ -14623,7 +14629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="826" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>15</v>
       </c>
@@ -14844,7 +14850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="839" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>15</v>
       </c>
@@ -14878,7 +14884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="841" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>15</v>
       </c>
@@ -14895,7 +14901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="842" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>15</v>
       </c>
@@ -14946,7 +14952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="845" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>15</v>
       </c>
@@ -15014,7 +15020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="849" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
         <v>15</v>
       </c>
@@ -15133,7 +15139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="856" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
         <v>15</v>
       </c>
@@ -15184,7 +15190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="859" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
         <v>15</v>
       </c>
@@ -15218,7 +15224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="861" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
         <v>15</v>
       </c>
@@ -15337,7 +15343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="868" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
         <v>15</v>
       </c>
@@ -15388,7 +15394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="871" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
         <v>15</v>
       </c>
@@ -15422,7 +15428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="873" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
         <v>15</v>
       </c>
@@ -15456,7 +15462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="875" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
         <v>15</v>
       </c>
@@ -15524,7 +15530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="879" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
         <v>15</v>
       </c>
@@ -15575,7 +15581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="882" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
         <v>15</v>
       </c>
@@ -15609,7 +15615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="884" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
         <v>15</v>
       </c>
@@ -15626,7 +15632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="885" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
         <v>15</v>
       </c>
@@ -15643,7 +15649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="886" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
         <v>15</v>
       </c>
@@ -15660,7 +15666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="887" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
         <v>15</v>
       </c>
@@ -15677,7 +15683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="888" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
         <v>15</v>
       </c>
@@ -15694,7 +15700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="889" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
         <v>15</v>
       </c>
@@ -15711,7 +15717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="890" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
         <v>15</v>
       </c>
@@ -15745,7 +15751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="892" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
         <v>15</v>
       </c>
@@ -15813,7 +15819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="896" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
         <v>15</v>
       </c>
@@ -15864,7 +15870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="899" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
         <v>15</v>
       </c>
@@ -15983,7 +15989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="906" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
         <v>15</v>
       </c>
@@ -16000,7 +16006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="907" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
         <v>15</v>
       </c>
@@ -16068,7 +16074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="911" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
         <v>15</v>
       </c>
@@ -16119,7 +16125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="914" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
         <v>15</v>
       </c>
@@ -16153,7 +16159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="916" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
         <v>15</v>
       </c>
@@ -16255,7 +16261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="922" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
         <v>15</v>
       </c>
@@ -16272,7 +16278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="923" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
         <v>15</v>
       </c>
@@ -16289,7 +16295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="924" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
         <v>15</v>
       </c>
@@ -16306,7 +16312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="925" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
         <v>15</v>
       </c>
@@ -16323,7 +16329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="926" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
         <v>15</v>
       </c>
@@ -16340,7 +16346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="927" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
         <v>15</v>
       </c>
@@ -16357,7 +16363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="928" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
         <v>15</v>
       </c>
@@ -16374,7 +16380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="929" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
         <v>15</v>
       </c>
@@ -16391,7 +16397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="930" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
         <v>15</v>
       </c>
@@ -16408,7 +16414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="931" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
         <v>15</v>
       </c>
@@ -16442,7 +16448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="933" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
         <v>15</v>
       </c>
@@ -16459,7 +16465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="934" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
         <v>15</v>
       </c>
@@ -16612,7 +16618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="943" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
         <v>15</v>
       </c>
@@ -16629,7 +16635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="944" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
         <v>15</v>
       </c>
@@ -16731,7 +16737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="950" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
         <v>15</v>
       </c>
@@ -16765,7 +16771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="952" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
         <v>15</v>
       </c>
@@ -16782,7 +16788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="953" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
         <v>15</v>
       </c>
@@ -16799,7 +16805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="954" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
         <v>15</v>
       </c>
@@ -16850,7 +16856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="957" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
         <v>15</v>
       </c>
@@ -16867,7 +16873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="958" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
         <v>15</v>
       </c>
@@ -16935,7 +16941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="962" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
         <v>15</v>
       </c>
@@ -16952,7 +16958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="963" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A963" t="s">
         <v>15</v>
       </c>
@@ -16969,7 +16975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="964" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
         <v>15</v>
       </c>
@@ -17054,7 +17060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="969" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
         <v>15</v>
       </c>
@@ -17105,7 +17111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="972" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
         <v>15</v>
       </c>
@@ -17190,7 +17196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="977" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
         <v>15</v>
       </c>
@@ -17207,7 +17213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="978" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
         <v>15</v>
       </c>
@@ -17275,7 +17281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="982" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
         <v>15</v>
       </c>
@@ -17326,7 +17332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="985" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
         <v>15</v>
       </c>
@@ -17411,7 +17417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="990" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
         <v>15</v>
       </c>
@@ -17445,7 +17451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="992" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
         <v>15</v>
       </c>
@@ -17479,7 +17485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="994" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
         <v>15</v>
       </c>
@@ -17564,7 +17570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="999" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
         <v>15</v>
       </c>
@@ -17581,7 +17587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1000" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
         <v>15</v>
       </c>
@@ -17615,7 +17621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1002" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
         <v>15</v>
       </c>
@@ -17785,7 +17791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1012" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
         <v>15</v>
       </c>
@@ -17802,7 +17808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1013" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
         <v>15</v>
       </c>
@@ -17819,7 +17825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1014" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
         <v>15</v>
       </c>
@@ -17853,7 +17859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1016" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
         <v>15</v>
       </c>
@@ -17989,7 +17995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1024" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
         <v>15</v>
       </c>
@@ -18006,7 +18012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1025" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1025" t="s">
         <v>15</v>
       </c>
@@ -18023,7 +18029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1026" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
         <v>15</v>
       </c>
@@ -18040,7 +18046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1027" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
         <v>15</v>
       </c>
@@ -18057,7 +18063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1028" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
         <v>15</v>
       </c>
@@ -18074,7 +18080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1029" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
         <v>15</v>
       </c>
@@ -18091,7 +18097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1030" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
         <v>15</v>
       </c>
@@ -18108,7 +18114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1031" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
         <v>15</v>
       </c>
@@ -18159,7 +18165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1034" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1034" t="s">
         <v>15</v>
       </c>
@@ -18193,7 +18199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1036" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
         <v>15</v>
       </c>
@@ -18210,7 +18216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1037" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
         <v>15</v>
       </c>
@@ -18244,7 +18250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1039" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1039" t="s">
         <v>15</v>
       </c>
@@ -18261,7 +18267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1040" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1040" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1040" t="s">
         <v>15</v>
       </c>
@@ -18278,7 +18284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1041" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1041" t="s">
         <v>15</v>
       </c>
@@ -18295,7 +18301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1042" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1042" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1042" t="s">
         <v>15</v>
       </c>
@@ -18312,7 +18318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1043" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1043" t="s">
         <v>15</v>
       </c>
@@ -18329,7 +18335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1044" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1044" t="s">
         <v>15</v>
       </c>
@@ -18346,7 +18352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1045" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1045" t="s">
         <v>15</v>
       </c>
@@ -18363,7 +18369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1046" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1046" t="s">
         <v>15</v>
       </c>
@@ -18380,7 +18386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1047" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1047" t="s">
         <v>15</v>
       </c>
@@ -18397,7 +18403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1048" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1048" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1048" t="s">
         <v>15</v>
       </c>
@@ -18414,7 +18420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1049" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1049" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1049" t="s">
         <v>15</v>
       </c>
@@ -18431,7 +18437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1050" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1050" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1050" t="s">
         <v>15</v>
       </c>
@@ -18550,7 +18556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1057" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1057" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1057" t="s">
         <v>15</v>
       </c>
@@ -18720,7 +18726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1067" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1067" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1067" t="s">
         <v>15</v>
       </c>
@@ -18771,7 +18777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1070" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1070" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1070" t="s">
         <v>15</v>
       </c>
@@ -18958,7 +18964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1081" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1081" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1081" t="s">
         <v>15</v>
       </c>
@@ -18992,7 +18998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1083" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1083" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1083" t="s">
         <v>15</v>
       </c>
@@ -19009,7 +19015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1084" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1084" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1084" t="s">
         <v>15</v>
       </c>
@@ -19043,7 +19049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1086" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1086" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1086" t="s">
         <v>15</v>
       </c>
@@ -19162,7 +19168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1093" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1093" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1093" t="s">
         <v>15</v>
       </c>
@@ -19196,7 +19202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1095" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1095" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1095" t="s">
         <v>15</v>
       </c>
@@ -19230,7 +19236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1097" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1097" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1097" t="s">
         <v>15</v>
       </c>
@@ -19247,7 +19253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1098" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1098" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1098" t="s">
         <v>15</v>
       </c>
@@ -19264,7 +19270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1099" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1099" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1099" t="s">
         <v>15</v>
       </c>
@@ -19281,7 +19287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1100" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1100" t="s">
         <v>15</v>
       </c>
@@ -19298,7 +19304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1101" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1101" t="s">
         <v>15</v>
       </c>
@@ -19332,7 +19338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1103" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1103" t="s">
         <v>15</v>
       </c>
@@ -19383,7 +19389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1106" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1106" t="s">
         <v>15</v>
       </c>
@@ -19400,7 +19406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1107" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1107" t="s">
         <v>15</v>
       </c>
@@ -19417,7 +19423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1108" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1108" t="s">
         <v>15</v>
       </c>
@@ -19553,7 +19559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1116" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1116" t="s">
         <v>15</v>
       </c>
@@ -19570,7 +19576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1117" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1117" t="s">
         <v>15</v>
       </c>
@@ -19638,7 +19644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1121" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1121" t="s">
         <v>15</v>
       </c>
@@ -19791,7 +19797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1130" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1130" t="s">
         <v>15</v>
       </c>
@@ -19808,7 +19814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1131" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1131" t="s">
         <v>15</v>
       </c>
@@ -19876,7 +19882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1135" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1135" t="s">
         <v>15</v>
       </c>
@@ -19893,7 +19899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1136" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1136" t="s">
         <v>15</v>
       </c>
@@ -19910,7 +19916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1137" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1137" t="s">
         <v>15</v>
       </c>
@@ -19978,7 +19984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1141" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1141" t="s">
         <v>15</v>
       </c>
@@ -20335,7 +20341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1162" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1162" t="s">
         <v>15</v>
       </c>
@@ -20386,7 +20392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1165" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1165" t="s">
         <v>15</v>
       </c>
@@ -20573,7 +20579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1176" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1176" t="s">
         <v>15</v>
       </c>
@@ -20777,7 +20783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1188" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1188" t="s">
         <v>15</v>
       </c>
@@ -20828,7 +20834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1191" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1191" t="s">
         <v>15</v>
       </c>
@@ -20896,7 +20902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1195" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1195" t="s">
         <v>15</v>
       </c>
@@ -21049,7 +21055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1204" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1204" t="s">
         <v>15</v>
       </c>
@@ -21202,7 +21208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1213" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1213" t="s">
         <v>15</v>
       </c>
@@ -21236,7 +21242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1215" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1215" t="s">
         <v>15</v>
       </c>
@@ -21321,7 +21327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1220" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1220" t="s">
         <v>15</v>
       </c>
@@ -21338,7 +21344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1221" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1221" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1221" t="s">
         <v>15</v>
       </c>
@@ -21355,7 +21361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1222" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1222" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1222" t="s">
         <v>15</v>
       </c>
@@ -21389,7 +21395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1224" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1224" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1224" t="s">
         <v>15</v>
       </c>
@@ -21440,7 +21446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1227" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1227" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1227" t="s">
         <v>15</v>
       </c>
@@ -21491,7 +21497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1230" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1230" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1230" t="s">
         <v>15</v>
       </c>
@@ -21695,7 +21701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1242" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1242" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1242" t="s">
         <v>15</v>
       </c>
@@ -21712,7 +21718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1243" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1243" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1243" t="s">
         <v>15</v>
       </c>
@@ -21814,7 +21820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1249" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1249" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1249" t="s">
         <v>18</v>
       </c>
@@ -21950,7 +21956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1257" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1257" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1257" t="s">
         <v>18</v>
       </c>
@@ -22018,7 +22024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1261" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1261" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1261" t="s">
         <v>18</v>
       </c>
@@ -22103,7 +22109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1266" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1266" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1266" t="s">
         <v>18</v>
       </c>
@@ -22120,7 +22126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1267" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1267" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1267" t="s">
         <v>18</v>
       </c>
@@ -22137,7 +22143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1268" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1268" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1268" t="s">
         <v>18</v>
       </c>
@@ -22154,7 +22160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1269" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1269" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1269" t="s">
         <v>18</v>
       </c>
@@ -22171,7 +22177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1270" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1270" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1270" t="s">
         <v>18</v>
       </c>
@@ -22188,7 +22194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1271" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1271" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1271" t="s">
         <v>18</v>
       </c>
@@ -22205,7 +22211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1272" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1272" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1272" t="s">
         <v>18</v>
       </c>
@@ -22222,7 +22228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1273" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1273" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1273" t="s">
         <v>18</v>
       </c>
@@ -22256,7 +22262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1275" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1275" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1275" t="s">
         <v>18</v>
       </c>
@@ -22273,7 +22279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1276" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1276" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1276" t="s">
         <v>18</v>
       </c>
@@ -22290,7 +22296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1277" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1277" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1277" t="s">
         <v>18</v>
       </c>
@@ -22324,7 +22330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1279" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1279" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1279" t="s">
         <v>18</v>
       </c>
@@ -22341,7 +22347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1280" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1280" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1280" t="s">
         <v>18</v>
       </c>
@@ -22358,7 +22364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1281" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1281" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1281" t="s">
         <v>18</v>
       </c>
@@ -22392,7 +22398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1283" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1283" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1283" t="s">
         <v>18</v>
       </c>
@@ -22409,7 +22415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1284" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1284" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1284" t="s">
         <v>18</v>
       </c>
@@ -22477,7 +22483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1288" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1288" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1288" t="s">
         <v>18</v>
       </c>
@@ -22698,7 +22704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1301" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1301" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1301" t="s">
         <v>18</v>
       </c>
@@ -22715,7 +22721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1302" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1302" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1302" t="s">
         <v>18</v>
       </c>
@@ -22732,7 +22738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1303" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1303" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1303" t="s">
         <v>18</v>
       </c>
@@ -22749,7 +22755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1304" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1304" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1304" t="s">
         <v>18</v>
       </c>
@@ -22766,7 +22772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1305" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1305" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1305" t="s">
         <v>18</v>
       </c>
@@ -22783,7 +22789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1306" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1306" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1306" t="s">
         <v>18</v>
       </c>
@@ -22800,7 +22806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1307" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1307" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1307" t="s">
         <v>18</v>
       </c>
@@ -22817,7 +22823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1308" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1308" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1308" t="s">
         <v>18</v>
       </c>
@@ -22834,7 +22840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1309" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1309" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1309" t="s">
         <v>18</v>
       </c>
@@ -22851,7 +22857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1310" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1310" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1310" t="s">
         <v>18</v>
       </c>
@@ -22868,7 +22874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1311" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1311" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1311" t="s">
         <v>18</v>
       </c>
@@ -22885,7 +22891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1312" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1312" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1312" t="s">
         <v>18</v>
       </c>
@@ -22902,7 +22908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1313" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1313" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1313" t="s">
         <v>18</v>
       </c>
@@ -22919,7 +22925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1314" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1314" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1314" t="s">
         <v>18</v>
       </c>
@@ -22936,7 +22942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1315" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1315" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1315" t="s">
         <v>18</v>
       </c>
@@ -22987,7 +22993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1318" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1318" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1318" t="s">
         <v>18</v>
       </c>
@@ -23072,7 +23078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1323" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1323" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1323" t="s">
         <v>18</v>
       </c>
@@ -23106,7 +23112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1325" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1325" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1325" t="s">
         <v>18</v>
       </c>
@@ -23293,7 +23299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1336" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1336" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1336" t="s">
         <v>18</v>
       </c>
@@ -23361,7 +23367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1340" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1340" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1340" t="s">
         <v>18</v>
       </c>
@@ -23429,7 +23435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1344" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1344" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1344" t="s">
         <v>18</v>
       </c>
@@ -23446,7 +23452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1345" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1345" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1345" t="s">
         <v>18</v>
       </c>
@@ -23463,7 +23469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1346" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1346" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1346" t="s">
         <v>18</v>
       </c>
@@ -23514,7 +23520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1349" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1349" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1349" t="s">
         <v>18</v>
       </c>
@@ -23531,7 +23537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1350" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1350" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1350" t="s">
         <v>18</v>
       </c>
@@ -23582,7 +23588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1353" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1353" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1353" t="s">
         <v>18</v>
       </c>
@@ -23599,7 +23605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1354" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1354" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1354" t="s">
         <v>18</v>
       </c>
@@ -23684,7 +23690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1359" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1359" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1359" t="s">
         <v>18</v>
       </c>
@@ -23905,7 +23911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1372" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1372" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1372" t="s">
         <v>18</v>
       </c>
@@ -24109,7 +24115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1384" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1384" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1384" t="s">
         <v>18</v>
       </c>
@@ -24143,7 +24149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1386" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1386" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1386" t="s">
         <v>18</v>
       </c>
@@ -24160,7 +24166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1387" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1387" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1387" t="s">
         <v>18</v>
       </c>
@@ -24177,7 +24183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1388" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1388" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1388" t="s">
         <v>18</v>
       </c>
@@ -24194,7 +24200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1389" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1389" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1389" t="s">
         <v>18</v>
       </c>
@@ -24211,7 +24217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1390" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1390" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1390" t="s">
         <v>18</v>
       </c>
@@ -24228,7 +24234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1391" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1391" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1391" t="s">
         <v>18</v>
       </c>
@@ -24245,7 +24251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1392" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1392" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1392" t="s">
         <v>18</v>
       </c>
@@ -24262,7 +24268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1393" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1393" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1393" t="s">
         <v>18</v>
       </c>
@@ -24296,7 +24302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1395" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1395" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1395" t="s">
         <v>18</v>
       </c>
@@ -24313,7 +24319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1396" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1396" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1396" t="s">
         <v>18</v>
       </c>
@@ -24330,7 +24336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1397" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1397" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1397" t="s">
         <v>18</v>
       </c>
@@ -24347,7 +24353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1398" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1398" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1398" t="s">
         <v>18</v>
       </c>
@@ -24364,7 +24370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1399" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1399" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1399" t="s">
         <v>18</v>
       </c>
@@ -24381,7 +24387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1400" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1400" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1400" t="s">
         <v>18</v>
       </c>
@@ -24483,7 +24489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1406" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1406" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1406" t="s">
         <v>18</v>
       </c>
@@ -24619,7 +24625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1414" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1414" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1414" t="s">
         <v>18</v>
       </c>
@@ -24772,7 +24778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1423" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1423" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1423" t="s">
         <v>18</v>
       </c>
@@ -24806,7 +24812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1425" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1425" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1425" t="s">
         <v>18</v>
       </c>
@@ -24823,7 +24829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1426" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1426" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1426" t="s">
         <v>18</v>
       </c>
@@ -25367,7 +25373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1458" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1458" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1458" t="s">
         <v>23</v>
       </c>
@@ -25469,7 +25475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1464" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1464" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1464" t="s">
         <v>23</v>
       </c>
@@ -25503,7 +25509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1466" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1466" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1466" t="s">
         <v>23</v>
       </c>
@@ -25537,7 +25543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1468" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1468" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1468" t="s">
         <v>23</v>
       </c>
@@ -26064,7 +26070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1499" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1499" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1499" t="s">
         <v>23</v>
       </c>
@@ -26285,7 +26291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1512" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1512" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1512" t="s">
         <v>23</v>
       </c>
@@ -26404,7 +26410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1519" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1519" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1519" t="s">
         <v>19</v>
       </c>
@@ -26421,7 +26427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1520" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1520" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1520" t="s">
         <v>19</v>
       </c>
@@ -26438,7 +26444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1521" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1521" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1521" t="s">
         <v>19</v>
       </c>
@@ -26472,7 +26478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1523" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1523" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1523" t="s">
         <v>19</v>
       </c>
@@ -26489,7 +26495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1524" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1524" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1524" t="s">
         <v>19</v>
       </c>
@@ -26591,7 +26597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1530" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1530" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1530" t="s">
         <v>19</v>
       </c>
@@ -26608,7 +26614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1531" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1531" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1531" t="s">
         <v>19</v>
       </c>
@@ -26625,7 +26631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1532" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1532" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1532" t="s">
         <v>19</v>
       </c>
@@ -26710,7 +26716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1537" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1537" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1537" t="s">
         <v>19</v>
       </c>
@@ -26761,7 +26767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1540" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1540" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1540" t="s">
         <v>19</v>
       </c>
@@ -26795,7 +26801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1542" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1542" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1542" t="s">
         <v>19</v>
       </c>
@@ -26812,7 +26818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1543" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1543" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1543" t="s">
         <v>19</v>
       </c>
@@ -26897,7 +26903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1548" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1548" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1548" t="s">
         <v>19</v>
       </c>
@@ -27101,7 +27107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1560" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1560" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1560" t="s">
         <v>19</v>
       </c>
@@ -27186,7 +27192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1565" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1565" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1565" t="s">
         <v>19</v>
       </c>
@@ -27203,7 +27209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1566" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1566" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1566" t="s">
         <v>19</v>
       </c>
@@ -27220,7 +27226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1567" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1567" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1567" t="s">
         <v>19</v>
       </c>
@@ -27271,7 +27277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1570" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1570" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1570" t="s">
         <v>19</v>
       </c>
@@ -27322,7 +27328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1573" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1573" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1573" t="s">
         <v>19</v>
       </c>
@@ -27339,7 +27345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1574" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1574" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1574" t="s">
         <v>19</v>
       </c>
@@ -27390,7 +27396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1577" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1577" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1577" t="s">
         <v>19</v>
       </c>
@@ -27424,7 +27430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1579" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1579" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1579" t="s">
         <v>19</v>
       </c>
@@ -27441,7 +27447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1580" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1580" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1580" t="s">
         <v>19</v>
       </c>
@@ -27509,7 +27515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1584" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1584" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1584" t="s">
         <v>19</v>
       </c>
@@ -27543,7 +27549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1586" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1586" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1586" t="s">
         <v>19</v>
       </c>
@@ -27594,7 +27600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1589" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1589" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1589" t="s">
         <v>19</v>
       </c>
@@ -27611,7 +27617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1590" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1590" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1590" t="s">
         <v>19</v>
       </c>
@@ -27628,7 +27634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1591" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1591" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1591" t="s">
         <v>19</v>
       </c>
@@ -27645,7 +27651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1592" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1592" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1592" t="s">
         <v>19</v>
       </c>
@@ -27662,7 +27668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1593" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1593" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1593" t="s">
         <v>19</v>
       </c>
@@ -27679,7 +27685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1594" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1594" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1594" t="s">
         <v>19</v>
       </c>
@@ -27696,7 +27702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1595" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1595" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1595" t="s">
         <v>19</v>
       </c>
@@ -27713,7 +27719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1596" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1596" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1596" t="s">
         <v>19</v>
       </c>
@@ -27900,7 +27906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1607" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1607" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1607" t="s">
         <v>19</v>
       </c>
@@ -27951,7 +27957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1610" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1610" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1610" t="s">
         <v>19</v>
       </c>
@@ -27968,7 +27974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1611" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1611" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1611" t="s">
         <v>19</v>
       </c>
@@ -27985,7 +27991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1612" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1612" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1612" t="s">
         <v>19</v>
       </c>
@@ -28036,7 +28042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1615" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1615" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1615" t="s">
         <v>19</v>
       </c>
@@ -28070,7 +28076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1617" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1617" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1617" t="s">
         <v>19</v>
       </c>
@@ -28172,7 +28178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1623" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1623" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1623" t="s">
         <v>19</v>
       </c>
@@ -28223,7 +28229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1626" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1626" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1626" t="s">
         <v>19</v>
       </c>
@@ -28444,7 +28450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1639" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1639" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1639" t="s">
         <v>19</v>
       </c>
@@ -28478,7 +28484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1641" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1641" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1641" t="s">
         <v>19</v>
       </c>
@@ -28495,7 +28501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1642" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1642" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1642" t="s">
         <v>19</v>
       </c>
@@ -28512,7 +28518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1643" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1643" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1643" t="s">
         <v>19</v>
       </c>
@@ -28546,7 +28552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1645" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1645" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1645" t="s">
         <v>19</v>
       </c>
@@ -28614,7 +28620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1649" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1649" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1649" t="s">
         <v>19</v>
       </c>
@@ -28937,7 +28943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1668" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1668" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1668" t="s">
         <v>19</v>
       </c>
@@ -29056,7 +29062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1675" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1675" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1675" t="s">
         <v>19</v>
       </c>
@@ -29226,7 +29232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1685" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1685" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1685" t="s">
         <v>19</v>
       </c>
@@ -29243,7 +29249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1686" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1686" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1686" t="s">
         <v>19</v>
       </c>
@@ -29260,7 +29266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1687" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1687" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1687" t="s">
         <v>19</v>
       </c>
@@ -29277,7 +29283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1688" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1688" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1688" t="s">
         <v>19</v>
       </c>
@@ -29617,7 +29623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1708" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1708" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1708" t="s">
         <v>19</v>
       </c>
@@ -29872,7 +29878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1723" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1723" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1723" t="s">
         <v>19</v>
       </c>
@@ -29957,7 +29963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1728" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1728" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1728" t="s">
         <v>19</v>
       </c>
@@ -29991,7 +29997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1730" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1730" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1730" t="s">
         <v>19</v>
       </c>
@@ -30008,7 +30014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1731" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1731" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1731" t="s">
         <v>19</v>
       </c>
@@ -30025,7 +30031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1732" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1732" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1732" t="s">
         <v>19</v>
       </c>
@@ -30059,7 +30065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1734" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1734" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1734" t="s">
         <v>19</v>
       </c>
@@ -30229,7 +30235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1744" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1744" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1744" t="s">
         <v>19</v>
       </c>
@@ -30263,7 +30269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1746" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1746" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1746" t="s">
         <v>19</v>
       </c>
@@ -30314,7 +30320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1749" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1749" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1749" t="s">
         <v>19</v>
       </c>
@@ -30433,7 +30439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1756" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1756" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1756" t="s">
         <v>19</v>
       </c>
@@ -30467,7 +30473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1758" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1758" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1758" t="s">
         <v>19</v>
       </c>
@@ -30501,7 +30507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1760" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1760" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1760" t="s">
         <v>19</v>
       </c>
@@ -30535,7 +30541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1762" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1762" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1762" t="s">
         <v>19</v>
       </c>
@@ -30552,7 +30558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1763" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1763" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1763" t="s">
         <v>19</v>
       </c>
@@ -30569,7 +30575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1764" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1764" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1764" t="s">
         <v>19</v>
       </c>
@@ -30603,7 +30609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1766" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1766" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1766" t="s">
         <v>19</v>
       </c>
@@ -30637,7 +30643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1768" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1768" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1768" t="s">
         <v>19</v>
       </c>
@@ -30705,7 +30711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1772" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1772" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1772" t="s">
         <v>19</v>
       </c>
@@ -30824,7 +30830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1779" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1779" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1779" t="s">
         <v>19</v>
       </c>
@@ -30875,7 +30881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1782" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1782" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1782" t="s">
         <v>19</v>
       </c>
@@ -30909,7 +30915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1784" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1784" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1784" t="s">
         <v>19</v>
       </c>
@@ -30926,7 +30932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1785" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1785" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1785" t="s">
         <v>19</v>
       </c>
@@ -30943,7 +30949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1786" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1786" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1786" t="s">
         <v>19</v>
       </c>
@@ -30960,7 +30966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1787" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1787" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1787" t="s">
         <v>19</v>
       </c>
@@ -31215,7 +31221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1802" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1802" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1802" t="s">
         <v>21</v>
       </c>
@@ -31232,7 +31238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1803" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1803" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1803" t="s">
         <v>21</v>
       </c>
@@ -31419,7 +31425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1814" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1814" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1814" t="s">
         <v>21</v>
       </c>
@@ -31453,7 +31459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1816" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1816" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1816" t="s">
         <v>21</v>
       </c>
@@ -31504,7 +31510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1819" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1819" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1819" t="s">
         <v>21</v>
       </c>
@@ -31538,7 +31544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1821" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1821" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1821" t="s">
         <v>21</v>
       </c>
@@ -31623,7 +31629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1826" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1826" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1826" t="s">
         <v>21</v>
       </c>
@@ -31640,7 +31646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1827" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1827" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1827" t="s">
         <v>21</v>
       </c>
@@ -31674,7 +31680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1829" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1829" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1829" t="s">
         <v>21</v>
       </c>
@@ -31725,7 +31731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1832" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1832" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1832" t="s">
         <v>21</v>
       </c>
@@ -31776,7 +31782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1835" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1835" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1835" t="s">
         <v>21</v>
       </c>
@@ -31827,7 +31833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1838" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1838" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1838" t="s">
         <v>21</v>
       </c>
@@ -31878,7 +31884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1841" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1841" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1841" t="s">
         <v>21</v>
       </c>
@@ -31895,7 +31901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1842" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1842" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1842" t="s">
         <v>21</v>
       </c>
@@ -31980,7 +31986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1847" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1847" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1847" t="s">
         <v>21</v>
       </c>
@@ -31997,7 +32003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1848" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1848" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1848" t="s">
         <v>21</v>
       </c>
@@ -32048,7 +32054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1851" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1851" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1851" t="s">
         <v>21</v>
       </c>
@@ -32082,7 +32088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1853" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1853" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1853" t="s">
         <v>21</v>
       </c>
@@ -32099,7 +32105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1854" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1854" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1854" t="s">
         <v>21</v>
       </c>
@@ -32116,7 +32122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1855" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1855" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1855" t="s">
         <v>21</v>
       </c>
@@ -32184,7 +32190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1859" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1859" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1859" t="s">
         <v>21</v>
       </c>
@@ -32218,7 +32224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1861" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1861" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1861" t="s">
         <v>21</v>
       </c>
@@ -32235,7 +32241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1862" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1862" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1862" t="s">
         <v>21</v>
       </c>
@@ -32252,7 +32258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1863" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1863" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1863" t="s">
         <v>21</v>
       </c>
@@ -32286,7 +32292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1865" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1865" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1865" t="s">
         <v>21</v>
       </c>
@@ -32303,7 +32309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1866" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1866" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1866" t="s">
         <v>21</v>
       </c>
@@ -32320,7 +32326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1867" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1867" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1867" t="s">
         <v>21</v>
       </c>
@@ -32405,7 +32411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1872" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1872" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1872" t="s">
         <v>21</v>
       </c>
@@ -32456,7 +32462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1875" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1875" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1875" t="s">
         <v>21</v>
       </c>
@@ -32473,7 +32479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1876" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1876" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1876" t="s">
         <v>21</v>
       </c>
@@ -32609,7 +32615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1884" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1884" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1884" t="s">
         <v>21</v>
       </c>
@@ -32626,7 +32632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1885" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1885" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1885" t="s">
         <v>21</v>
       </c>
@@ -32643,7 +32649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1886" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1886" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1886" t="s">
         <v>21</v>
       </c>
@@ -32660,7 +32666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1887" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1887" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1887" t="s">
         <v>21</v>
       </c>
@@ -32677,7 +32683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1888" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1888" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1888" t="s">
         <v>21</v>
       </c>
@@ -32694,7 +32700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1889" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1889" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1889" t="s">
         <v>21</v>
       </c>
@@ -32745,7 +32751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1892" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1892" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1892" t="s">
         <v>21</v>
       </c>
@@ -32762,7 +32768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1893" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1893" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1893" t="s">
         <v>21</v>
       </c>
@@ -32779,7 +32785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1894" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1894" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1894" t="s">
         <v>21</v>
       </c>
@@ -32796,7 +32802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1895" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1895" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1895" t="s">
         <v>21</v>
       </c>
@@ -32813,7 +32819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1896" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1896" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1896" t="s">
         <v>21</v>
       </c>
@@ -32847,7 +32853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1898" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1898" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1898" t="s">
         <v>21</v>
       </c>
@@ -32864,7 +32870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1899" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1899" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1899" t="s">
         <v>21</v>
       </c>
@@ -32881,7 +32887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1900" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1900" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1900" t="s">
         <v>21</v>
       </c>
@@ -32898,7 +32904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1901" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1901" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1901" t="s">
         <v>21</v>
       </c>
@@ -32915,7 +32921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1902" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1902" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1902" t="s">
         <v>21</v>
       </c>
@@ -32932,7 +32938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1903" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1903" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1903" t="s">
         <v>21</v>
       </c>
@@ -32949,7 +32955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1904" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1904" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1904" t="s">
         <v>21</v>
       </c>
@@ -32966,7 +32972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1905" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1905" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1905" t="s">
         <v>21</v>
       </c>
@@ -32983,7 +32989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1906" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1906" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1906" t="s">
         <v>21</v>
       </c>
@@ -33000,7 +33006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1907" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1907" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1907" t="s">
         <v>21</v>
       </c>
@@ -33017,7 +33023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1908" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1908" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1908" t="s">
         <v>21</v>
       </c>
@@ -33034,7 +33040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1909" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1909" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1909" t="s">
         <v>21</v>
       </c>
@@ -33051,7 +33057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1910" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1910" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1910" t="s">
         <v>21</v>
       </c>
@@ -33068,7 +33074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1911" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1911" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1911" t="s">
         <v>21</v>
       </c>
@@ -33085,7 +33091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1912" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1912" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1912" t="s">
         <v>21</v>
       </c>
@@ -33102,7 +33108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1913" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1913" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1913" t="s">
         <v>21</v>
       </c>
@@ -33119,7 +33125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1914" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1914" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1914" t="s">
         <v>21</v>
       </c>
@@ -33136,7 +33142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1915" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1915" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1915" t="s">
         <v>21</v>
       </c>
@@ -33153,7 +33159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1916" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1916" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1916" t="s">
         <v>21</v>
       </c>
@@ -33204,7 +33210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1919" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1919" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1919" t="s">
         <v>21</v>
       </c>
@@ -33272,7 +33278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1923" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1923" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1923" t="s">
         <v>21</v>
       </c>
@@ -33306,7 +33312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1925" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1925" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1925" t="s">
         <v>21</v>
       </c>
@@ -33323,7 +33329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1926" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1926" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1926" t="s">
         <v>21</v>
       </c>
@@ -33340,7 +33346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1927" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1927" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1927" t="s">
         <v>21</v>
       </c>
@@ -33357,7 +33363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1928" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1928" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1928" t="s">
         <v>21</v>
       </c>
@@ -33374,7 +33380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1929" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1929" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1929" t="s">
         <v>21</v>
       </c>
@@ -33391,7 +33397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1930" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1930" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1930" t="s">
         <v>21</v>
       </c>
@@ -33408,7 +33414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1931" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1931" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1931" t="s">
         <v>21</v>
       </c>
@@ -33425,7 +33431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1932" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1932" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1932" t="s">
         <v>21</v>
       </c>
@@ -33595,7 +33601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1942" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1942" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1942" t="s">
         <v>21</v>
       </c>
@@ -33748,7 +33754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1951" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1951" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1951" t="s">
         <v>21</v>
       </c>
@@ -33782,7 +33788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1953" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1953" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1953" t="s">
         <v>21</v>
       </c>
@@ -33799,7 +33805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1954" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1954" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1954" t="s">
         <v>21</v>
       </c>
@@ -33884,7 +33890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1959" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1959" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1959" t="s">
         <v>21</v>
       </c>
@@ -33918,7 +33924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1961" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1961" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1961" t="s">
         <v>21</v>
       </c>
@@ -34003,7 +34009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1966" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1966" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1966" t="s">
         <v>21</v>
       </c>
@@ -34020,7 +34026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1967" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1967" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1967" t="s">
         <v>21</v>
       </c>
@@ -34088,7 +34094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1971" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1971" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1971" t="s">
         <v>21</v>
       </c>
@@ -34530,7 +34536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1997" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1997" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1997" t="s">
         <v>21</v>
       </c>
@@ -34836,7 +34842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2015" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2015" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2015" t="s">
         <v>21</v>
       </c>
@@ -34870,7 +34876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2017" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2017" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2017" t="s">
         <v>21</v>
       </c>
@@ -34921,7 +34927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2020" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2020" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2020" t="s">
         <v>21</v>
       </c>
@@ -34938,7 +34944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2021" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2021" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2021" t="s">
         <v>21</v>
       </c>
@@ -34955,7 +34961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2022" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2022" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2022" t="s">
         <v>21</v>
       </c>
@@ -34972,7 +34978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2023" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2023" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2023" t="s">
         <v>21</v>
       </c>
@@ -34989,7 +34995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2024" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2024" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2024" t="s">
         <v>21</v>
       </c>
@@ -35006,7 +35012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2025" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2025" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2025" t="s">
         <v>21</v>
       </c>
@@ -35210,7 +35216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2037" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2037" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2037" t="s">
         <v>21</v>
       </c>
@@ -35261,7 +35267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2040" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2040" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2040" t="s">
         <v>21</v>
       </c>
@@ -35380,7 +35386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2047" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2047" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2047" t="s">
         <v>21</v>
       </c>
@@ -35669,7 +35675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2064" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2064" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2064" t="s">
         <v>21</v>
       </c>
@@ -35720,7 +35726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2067" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2067" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2067" t="s">
         <v>21</v>
       </c>
@@ -35805,7 +35811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2072" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2072" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2072" t="s">
         <v>21</v>
       </c>
@@ -35839,7 +35845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2074" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2074" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2074" t="s">
         <v>21</v>
       </c>
@@ -35856,7 +35862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2075" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2075" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2075" t="s">
         <v>21</v>
       </c>
@@ -35958,7 +35964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2081" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2081" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2081" t="s">
         <v>21</v>
       </c>
@@ -35975,7 +35981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2082" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2082" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2082" t="s">
         <v>21</v>
       </c>
@@ -35992,7 +35998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2083" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2083" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2083" t="s">
         <v>21</v>
       </c>
@@ -36026,7 +36032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2085" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2085" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2085" t="s">
         <v>21</v>
       </c>
@@ -36060,7 +36066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2087" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2087" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2087" t="s">
         <v>21</v>
       </c>
@@ -36111,7 +36117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2090" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2090" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2090" t="s">
         <v>21</v>
       </c>
@@ -36213,7 +36219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2096" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2096" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2096" t="s">
         <v>21</v>
       </c>
@@ -36230,7 +36236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2097" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2097" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2097" t="s">
         <v>21</v>
       </c>
@@ -36587,7 +36593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2118" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2118" t="s">
         <v>21</v>
       </c>
@@ -36655,7 +36661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2122" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2122" t="s">
         <v>21</v>
       </c>
@@ -36672,7 +36678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2123" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2123" t="s">
         <v>21</v>
       </c>
@@ -36689,7 +36695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2124" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2124" t="s">
         <v>21</v>
       </c>
@@ -36723,7 +36729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2126" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2126" t="s">
         <v>21</v>
       </c>
@@ -36740,7 +36746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2127" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2127" t="s">
         <v>21</v>
       </c>
@@ -36757,7 +36763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2128" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2128" t="s">
         <v>21</v>
       </c>
@@ -36842,7 +36848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2133" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2133" t="s">
         <v>21</v>
       </c>
@@ -37063,7 +37069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2146" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2146" t="s">
         <v>21</v>
       </c>
@@ -37386,7 +37392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2165" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2165" t="s">
         <v>20</v>
       </c>
@@ -37675,7 +37681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2182" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2182" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2182" t="s">
         <v>20</v>
       </c>
@@ -37692,7 +37698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2183" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2183" t="s">
         <v>20</v>
       </c>
@@ -37726,7 +37732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2185" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2185" t="s">
         <v>20</v>
       </c>
@@ -37743,7 +37749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2186" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2186" t="s">
         <v>20</v>
       </c>
@@ -37811,7 +37817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2190" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2190" t="s">
         <v>20</v>
       </c>
@@ -37862,7 +37868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2193" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2193" t="s">
         <v>20</v>
       </c>
@@ -37879,7 +37885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2194" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2194" t="s">
         <v>20</v>
       </c>
@@ -38015,7 +38021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2202" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2202" t="s">
         <v>20</v>
       </c>
@@ -38049,7 +38055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2204" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2204" t="s">
         <v>20</v>
       </c>
@@ -38066,7 +38072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2205" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2205" t="s">
         <v>20</v>
       </c>
@@ -38083,7 +38089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2206" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2206" t="s">
         <v>20</v>
       </c>
@@ -38100,7 +38106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2207" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2207" t="s">
         <v>20</v>
       </c>
@@ -38117,7 +38123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2208" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2208" t="s">
         <v>20</v>
       </c>
@@ -38151,7 +38157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2210" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2210" t="s">
         <v>20</v>
       </c>
@@ -38168,7 +38174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2211" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2211" t="s">
         <v>20</v>
       </c>
@@ -38185,7 +38191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2212" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2212" t="s">
         <v>20</v>
       </c>
@@ -38202,7 +38208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2213" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2213" t="s">
         <v>20</v>
       </c>
@@ -38253,7 +38259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2216" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2216" t="s">
         <v>20</v>
       </c>
@@ -38355,7 +38361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2222" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2222" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2222" t="s">
         <v>20</v>
       </c>
@@ -38457,7 +38463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2228" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2228" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2228" t="s">
         <v>20</v>
       </c>
@@ -38474,7 +38480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2229" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2229" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2229" t="s">
         <v>20</v>
       </c>
@@ -38508,7 +38514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2231" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2231" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2231" t="s">
         <v>20</v>
       </c>
@@ -38542,7 +38548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2233" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2233" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2233" t="s">
         <v>20</v>
       </c>
@@ -38576,7 +38582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2235" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2235" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2235" t="s">
         <v>20</v>
       </c>
@@ -38593,7 +38599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2236" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2236" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2236" t="s">
         <v>20</v>
       </c>
@@ -38661,7 +38667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2240" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2240" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2240" t="s">
         <v>20</v>
       </c>
@@ -38712,7 +38718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2243" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2243" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2243" t="s">
         <v>20</v>
       </c>
@@ -38729,7 +38735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2244" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2244" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2244" t="s">
         <v>20</v>
       </c>
@@ -38848,7 +38854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2251" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2251" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2251" t="s">
         <v>20</v>
       </c>
@@ -38865,7 +38871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2252" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2252" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2252" t="s">
         <v>20</v>
       </c>
@@ -38916,7 +38922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2255" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2255" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2255" t="s">
         <v>20</v>
       </c>
@@ -38933,7 +38939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2256" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2256" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2256" t="s">
         <v>20</v>
       </c>
@@ -39001,7 +39007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2260" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2260" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2260" t="s">
         <v>20</v>
       </c>
@@ -39035,7 +39041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2262" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2262" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2262" t="s">
         <v>20</v>
       </c>
@@ -39052,7 +39058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2263" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2263" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2263" t="s">
         <v>20</v>
       </c>
@@ -39086,7 +39092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2265" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2265" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2265" t="s">
         <v>20</v>
       </c>
@@ -39103,7 +39109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2266" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2266" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2266" t="s">
         <v>20</v>
       </c>
@@ -39154,7 +39160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2269" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2269" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2269" t="s">
         <v>20</v>
       </c>
